--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INMOBILIARIA GÁLVEZ SANTA CRUZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_INMOBILIARIA GÁLVEZ SANTA CRUZ.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>40.5386</v>
+        <v>43.9922</v>
       </c>
       <c r="E2" t="n">
-        <v>40.89</v>
+        <v>44.717</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3515000000000008</v>
+        <v>-0.7244999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>43.2648</v>
@@ -610,13 +610,13 @@
         <v>48.6556</v>
       </c>
       <c r="S2" t="n">
-        <v>-10.6446</v>
+        <v>-7.1907</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.5686</v>
+        <v>-3.7414</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.0762</v>
+        <v>-3.449</v>
       </c>
       <c r="V2" t="n">
         <v>19.8886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. EDOMWONYI IBRAHIM</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>32.7523</v>
+        <v>35.1916</v>
       </c>
       <c r="E3" t="n">
-        <v>38.4466</v>
+        <v>38.9385</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.694099999999999</v>
+        <v>-3.747100000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>25.3292</v>
+        <v>7.008499999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>25.8663</v>
+        <v>19.1783</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5368999999999993</v>
+        <v>-12.1699</v>
       </c>
       <c r="J3" t="n">
-        <v>43.6864</v>
+        <v>43.1157</v>
       </c>
       <c r="K3" t="n">
-        <v>40.7091</v>
+        <v>43.2664</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9778</v>
+        <v>-0.1505000000000005</v>
       </c>
       <c r="M3" t="n">
-        <v>-18.357</v>
+        <v>-36.1075</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.8428</v>
+        <v>-24.0883</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.514699999999999</v>
+        <v>-12.0191</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3516</v>
+        <v>-5.213200000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-34.1752</v>
+        <v>-47.4975</v>
       </c>
       <c r="R3" t="n">
-        <v>35.5265</v>
+        <v>42.2839</v>
       </c>
       <c r="S3" t="n">
-        <v>27.8962</v>
+        <v>-7.0528</v>
       </c>
       <c r="T3" t="n">
-        <v>24.979</v>
+        <v>-4.704899999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9174</v>
+        <v>-2.3479</v>
       </c>
       <c r="V3" t="n">
-        <v>-21.8249</v>
+        <v>40.449</v>
       </c>
       <c r="W3" t="n">
-        <v>3.9558</v>
+        <v>48.0249</v>
       </c>
       <c r="X3" t="n">
-        <v>-25.7808</v>
+        <v>-7.5759</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>29.5479</v>
+        <v>14.5874</v>
       </c>
       <c r="E4" t="n">
-        <v>32.1607</v>
+        <v>13.4658</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6128</v>
+        <v>1.1215</v>
       </c>
       <c r="G4" t="n">
-        <v>7.008499999999998</v>
+        <v>-11.8946</v>
       </c>
       <c r="H4" t="n">
-        <v>19.1783</v>
+        <v>-11.4794</v>
       </c>
       <c r="I4" t="n">
-        <v>-12.1699</v>
+        <v>-0.4148000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>43.1157</v>
+        <v>21.2238</v>
       </c>
       <c r="K4" t="n">
-        <v>43.2664</v>
+        <v>9.8521</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1505000000000005</v>
+        <v>11.3716</v>
       </c>
       <c r="M4" t="n">
-        <v>-36.1075</v>
+        <v>-33.1182</v>
       </c>
       <c r="N4" t="n">
-        <v>-24.0883</v>
+        <v>-21.3315</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.0191</v>
+        <v>-11.7866</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.213200000000001</v>
+        <v>20.8524</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.4975</v>
+        <v>-28.5758</v>
       </c>
       <c r="R4" t="n">
-        <v>42.2839</v>
+        <v>49.4278</v>
       </c>
       <c r="S4" t="n">
-        <v>-12.6963</v>
+        <v>-8.4884</v>
       </c>
       <c r="T4" t="n">
-        <v>-11.4826</v>
+        <v>-3.8511</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2136</v>
+        <v>-4.636900000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>40.449</v>
+        <v>14.1175</v>
       </c>
       <c r="W4" t="n">
-        <v>48.0249</v>
+        <v>24.6689</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.5759</v>
+        <v>-10.5514</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VERA PEIRO</t>
+          <t>I. EDOMWONYI IBRAHIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>4.569100000000001</v>
+        <v>13.5042</v>
       </c>
       <c r="E5" t="n">
-        <v>17.681</v>
+        <v>20.8238</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.1124</v>
+        <v>-7.319700000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>16.3776</v>
+        <v>25.3292</v>
       </c>
       <c r="H5" t="n">
-        <v>21.2821</v>
+        <v>25.8663</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.904200000000001</v>
+        <v>-0.5368999999999993</v>
       </c>
       <c r="J5" t="n">
-        <v>48.3835</v>
+        <v>43.6864</v>
       </c>
       <c r="K5" t="n">
-        <v>39.3017</v>
+        <v>40.7091</v>
       </c>
       <c r="L5" t="n">
-        <v>9.081799999999999</v>
+        <v>2.9778</v>
       </c>
       <c r="M5" t="n">
-        <v>-32.0058</v>
+        <v>-18.357</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.0193</v>
+        <v>-14.8428</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.9861</v>
+        <v>-3.514699999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-13.9018</v>
+        <v>1.3516</v>
       </c>
       <c r="Q5" t="n">
-        <v>-55.9931</v>
+        <v>-34.1752</v>
       </c>
       <c r="R5" t="n">
-        <v>42.0912</v>
+        <v>35.5265</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0867</v>
+        <v>8.6479</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4025</v>
+        <v>7.3563</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.316</v>
+        <v>1.2913</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0059</v>
+        <v>-21.8249</v>
       </c>
       <c r="W5" t="n">
-        <v>20.8877</v>
+        <v>3.9558</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.8817</v>
+        <v>-25.7808</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U. JORDAN DIAZ</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2387</v>
+        <v>3.9781</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.397</v>
+        <v>6.303500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6357</v>
+        <v>-2.3254</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6206</v>
+        <v>-3.361000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0621</v>
+        <v>-5.0525</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6827</v>
+        <v>1.6914</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6274</v>
+        <v>11.9201</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0621</v>
+        <v>1.2308</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6895</v>
+        <v>10.6891</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0068</v>
+        <v>-15.2809</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-6.2829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0068</v>
+        <v>-8.997900000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3862</v>
+        <v>7.723</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-10.2333</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>17.9562</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1876</v>
+        <v>-0.7030000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0552</v>
+        <v>-1.4789</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2428</v>
+        <v>0.7765</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2856</v>
+        <v>0.3189000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2856</v>
+        <v>6.0958</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-5.7769</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DÉNIZ LUZARDO</t>
+          <t>A. VERA PEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1005</v>
+        <v>2.386600000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>13.4963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1005</v>
+        <v>-11.1097</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>16.3776</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>21.2821</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-4.904200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>48.3835</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>39.3017</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>9.081799999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-32.0058</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-18.0193</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-13.9861</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>-13.9018</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-55.9931</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>42.0912</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1.0953</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.2176999999999997</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-1.3133</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2856</v>
+        <v>1.0059</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>20.8877</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>-19.8817</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1237000000000004</v>
+        <v>0.6057000000000011</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0003</v>
+        <v>13.4569</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.124099999999999</v>
+        <v>-12.8513</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.361000000000001</v>
+        <v>15.3724</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.0525</v>
+        <v>22.0325</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6914</v>
+        <v>-6.660100000000002</v>
       </c>
       <c r="J8" t="n">
-        <v>11.9201</v>
+        <v>43.4398</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2308</v>
+        <v>35.7026</v>
       </c>
       <c r="L8" t="n">
-        <v>10.6891</v>
+        <v>7.737</v>
       </c>
       <c r="M8" t="n">
-        <v>-15.2809</v>
+        <v>-28.0673</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.2829</v>
+        <v>-13.6703</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.997900000000001</v>
+        <v>-14.3974</v>
       </c>
       <c r="P8" t="n">
-        <v>7.723</v>
+        <v>-15.2532</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.2333</v>
+        <v>-48.0767</v>
       </c>
       <c r="R8" t="n">
-        <v>17.9562</v>
+        <v>32.8231</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.8043</v>
+        <v>0.9463000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.7821</v>
+        <v>-1.7795</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0221</v>
+        <v>2.7256</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3189000000000001</v>
+        <v>-0.4594999999999994</v>
       </c>
       <c r="W8" t="n">
-        <v>6.0958</v>
+        <v>19.8734</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.7769</v>
+        <v>-20.3327</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>U. JORDAN DIAZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3519</v>
+        <v>0.4994</v>
       </c>
       <c r="E9" t="n">
-        <v>3.736999999999998</v>
+        <v>-0.0867</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.0889</v>
+        <v>0.5861</v>
       </c>
       <c r="G9" t="n">
-        <v>-11.8946</v>
+        <v>-0.6206</v>
       </c>
       <c r="H9" t="n">
-        <v>-11.4794</v>
+        <v>0.0621</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4148000000000001</v>
+        <v>-0.6827</v>
       </c>
       <c r="J9" t="n">
-        <v>21.2238</v>
+        <v>-0.6274</v>
       </c>
       <c r="K9" t="n">
-        <v>9.8521</v>
+        <v>0.0621</v>
       </c>
       <c r="L9" t="n">
-        <v>11.3716</v>
+        <v>-0.6895</v>
       </c>
       <c r="M9" t="n">
-        <v>-33.1182</v>
+        <v>0.0068</v>
       </c>
       <c r="N9" t="n">
-        <v>-21.3315</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-11.7866</v>
+        <v>0.0068</v>
       </c>
       <c r="P9" t="n">
-        <v>20.8524</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-28.5758</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>49.4278</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-24.4272</v>
+        <v>0.4482</v>
       </c>
       <c r="T9" t="n">
-        <v>-13.5803</v>
+        <v>0.2551</v>
       </c>
       <c r="U9" t="n">
-        <v>-10.8472</v>
+        <v>0.1931</v>
       </c>
       <c r="V9" t="n">
-        <v>14.1175</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>24.6689</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-10.5514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SOW SOW</t>
+          <t>J. DÉNIZ LUZARDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4919</v>
+        <v>0.204</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3585</v>
+        <v>0.1034</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1334</v>
+        <v>0.1005</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7865</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5237999999999999</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3104</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.303</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.076</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.379</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4836</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5521999999999999</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9314</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2153</v>
+        <v>0.1034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.05550000000000002</v>
+        <v>0.1034</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1598</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. HERNÁNDEZ DELGADO</t>
+          <t>M. SOW SOW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6142</v>
+        <v>-2.1112</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3945</v>
+        <v>-0.1516</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2198</v>
+        <v>-1.9597</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5676</v>
+        <v>-1.7865</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1174</v>
+        <v>0.5237999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-2.3104</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.243</v>
+        <v>-0.303</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3244</v>
+        <v>1.076</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5674</v>
+        <v>-1.379</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3247</v>
+        <v>-1.4836</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2071</v>
+        <v>-0.5521999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1176</v>
+        <v>-0.9314</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.502</v>
+        <v>0.1653</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2207</v>
+        <v>0.1513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2813</v>
+        <v>0.014</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>I. HERNÁNDEZ DELGADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0346</v>
+        <v>-2.1743</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2827</v>
+        <v>-2.2911</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2481</v>
+        <v>0.1168</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2062</v>
+        <v>-0.5676</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1815</v>
+        <v>0.1174</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0247</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3236000000000002</v>
+        <v>-0.243</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7184</v>
+        <v>0.3244</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3944</v>
+        <v>-0.5674</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.5301</v>
+        <v>-0.3247</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.8998</v>
+        <v>-0.2071</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6302</v>
+        <v>-0.1176</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6339</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.2478</v>
+        <v>-1.9308</v>
       </c>
       <c r="R12" t="n">
-        <v>8.8817</v>
+        <v>0.3862</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3128</v>
+        <v>-0.062</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9878</v>
+        <v>-0.1173</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6751</v>
+        <v>0.0553</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.1494</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1755</v>
+        <v>-2.7494</v>
       </c>
       <c r="E13" t="n">
-        <v>6.3759</v>
+        <v>-4.9861</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.551</v>
+        <v>2.2371</v>
       </c>
       <c r="G13" t="n">
-        <v>15.3724</v>
+        <v>-4.2062</v>
       </c>
       <c r="H13" t="n">
-        <v>22.0325</v>
+        <v>-1.1815</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.660100000000002</v>
+        <v>-3.0247</v>
       </c>
       <c r="J13" t="n">
-        <v>43.4398</v>
+        <v>0.3236000000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>35.7026</v>
+        <v>1.7184</v>
       </c>
       <c r="L13" t="n">
-        <v>7.737</v>
+        <v>-1.3944</v>
       </c>
       <c r="M13" t="n">
-        <v>-28.0673</v>
+        <v>-4.5301</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.6703</v>
+        <v>-2.8998</v>
       </c>
       <c r="O13" t="n">
-        <v>-14.3974</v>
+        <v>-1.6302</v>
       </c>
       <c r="P13" t="n">
-        <v>-15.2532</v>
+        <v>4.6339</v>
       </c>
       <c r="Q13" t="n">
-        <v>-48.0767</v>
+        <v>-4.2478</v>
       </c>
       <c r="R13" t="n">
-        <v>32.8231</v>
+        <v>8.8817</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8348</v>
+        <v>-0.02759999999999996</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.860900000000001</v>
+        <v>-0.6916</v>
       </c>
       <c r="U13" t="n">
-        <v>4.025700000000001</v>
+        <v>0.6639999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4594999999999994</v>
+        <v>-3.1494</v>
       </c>
       <c r="W13" t="n">
-        <v>19.8734</v>
+        <v>-0.3709</v>
       </c>
       <c r="X13" t="n">
-        <v>-20.3327</v>
+        <v>-2.7785</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.164499999999999</v>
+        <v>-3.672800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.7611</v>
+        <v>-11.0777</v>
       </c>
       <c r="F14" t="n">
-        <v>4.596299999999999</v>
+        <v>7.4051</v>
       </c>
       <c r="G14" t="n">
         <v>-2.7595</v>
@@ -1546,13 +1546,13 @@
         <v>22.5899</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.5805</v>
+        <v>-5.0886</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1635</v>
+        <v>-1.4805</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.4168</v>
+        <v>-3.6084</v>
       </c>
       <c r="V14" t="n">
         <v>0.6997999999999998</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>P. JIMÉNEZ VELÁZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.2898</v>
+        <v>-8.700099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.7407</v>
+        <v>-4.901</v>
       </c>
       <c r="F15" t="n">
-        <v>2.451</v>
+        <v>-3.7991</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.1303</v>
+        <v>-9.0837</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.9531</v>
+        <v>-4.8766</v>
       </c>
       <c r="I15" t="n">
-        <v>-8.177099999999999</v>
+        <v>-4.207</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4065</v>
+        <v>-2.2102</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0836</v>
+        <v>-1.288</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3228</v>
+        <v>-0.9221000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-11.7238</v>
+        <v>-6.8733</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.8693</v>
+        <v>-3.5886</v>
       </c>
       <c r="O15" t="n">
-        <v>-7.8542</v>
+        <v>-3.2848</v>
       </c>
       <c r="P15" t="n">
-        <v>5.0202</v>
+        <v>3.6686</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.3226</v>
+        <v>-2.317</v>
       </c>
       <c r="R15" t="n">
-        <v>18.3425</v>
+        <v>5.9856</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9001</v>
+        <v>0.02729999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3326</v>
+        <v>-0.374</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5676000000000001</v>
+        <v>0.4012</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.0794</v>
+        <v>-3.3122</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6557</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.7351</v>
+        <v>-3.3122</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-6.3664</v>
+        <v>-9.003500000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.1802</v>
+        <v>-11.9261</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1862</v>
+        <v>2.9223</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00360000000000027</v>
+        <v>-13.1303</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0397</v>
+        <v>-4.9531</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0434</v>
+        <v>-8.177099999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>7.7348</v>
+        <v>-1.4065</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1365</v>
+        <v>-1.0836</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5983</v>
+        <v>-0.3228</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.731199999999999</v>
+        <v>-11.7238</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.1764</v>
+        <v>-3.8693</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.5549</v>
+        <v>-7.8542</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.8961</v>
+        <v>5.0202</v>
       </c>
       <c r="Q16" t="n">
-        <v>-14.0948</v>
+        <v>-13.3226</v>
       </c>
       <c r="R16" t="n">
-        <v>11.1986</v>
+        <v>18.3425</v>
       </c>
       <c r="S16" t="n">
-        <v>7.364699999999999</v>
+        <v>1.1859</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4927</v>
+        <v>0.1471</v>
       </c>
       <c r="U16" t="n">
-        <v>2.8722</v>
+        <v>1.0389</v>
       </c>
       <c r="V16" t="n">
-        <v>-10.8385</v>
+        <v>-2.0794</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.3129</v>
+        <v>2.6557</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.525600000000001</v>
+        <v>-4.7351</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. JIMÉNEZ VELÁZQUEZ</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.2597</v>
+        <v>-11.6971</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.9904</v>
+        <v>-6.6895</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.2696</v>
+        <v>-5.0076</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.0837</v>
+        <v>0.00360000000000027</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.8766</v>
+        <v>-2.0397</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.207</v>
+        <v>2.0434</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.2102</v>
+        <v>7.7348</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.288</v>
+        <v>3.1365</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9221000000000001</v>
+        <v>4.5983</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.8733</v>
+        <v>-7.731199999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.5886</v>
+        <v>-5.1764</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.2848</v>
+        <v>-2.5549</v>
       </c>
       <c r="P17" t="n">
-        <v>3.6686</v>
+        <v>-2.8961</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.317</v>
+        <v>-14.0948</v>
       </c>
       <c r="R17" t="n">
-        <v>5.9856</v>
+        <v>11.1986</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5325</v>
+        <v>2.0341</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4634</v>
+        <v>0.9833000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0691</v>
+        <v>1.0508</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.3122</v>
+        <v>-10.8385</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1.3129</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.3122</v>
+        <v>-9.525600000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. QUINTERO HURTADO</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-14.7585</v>
+        <v>-12.4025</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.0167</v>
+        <v>-5.694500000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7419</v>
+        <v>-6.7082</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.3226</v>
+        <v>-13.7041</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5462</v>
+        <v>-6.4207</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.7763</v>
+        <v>-7.2835</v>
       </c>
       <c r="J18" t="n">
-        <v>-8.2218</v>
+        <v>7.932899999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6976</v>
+        <v>6.969</v>
       </c>
       <c r="L18" t="n">
-        <v>-9.9193</v>
+        <v>0.9635999999999998</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.1007</v>
+        <v>-21.6371</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.2438</v>
+        <v>-13.3896</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.857</v>
+        <v>-8.2476</v>
       </c>
       <c r="P18" t="n">
-        <v>2.51</v>
+        <v>11.0056</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.317</v>
+        <v>-12.7433</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8269</v>
+        <v>23.7486</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.819</v>
+        <v>-3.896</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4354</v>
+        <v>-2.3974</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3836</v>
+        <v>-1.4983</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.1272</v>
+        <v>-5.807700000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0426</v>
+        <v>1.5133</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.0845</v>
+        <v>-7.321000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. QUINTERO HURTADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>-19.1818</v>
+        <v>-12.988</v>
       </c>
       <c r="E19" t="n">
-        <v>-8.376799999999999</v>
+        <v>-10.9824</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.8047</v>
+        <v>-2.0054</v>
       </c>
       <c r="G19" t="n">
-        <v>-13.7041</v>
+        <v>-12.3226</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.4207</v>
+        <v>-1.5462</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.2835</v>
+        <v>-10.7763</v>
       </c>
       <c r="J19" t="n">
-        <v>7.932899999999999</v>
+        <v>-8.2218</v>
       </c>
       <c r="K19" t="n">
-        <v>6.969</v>
+        <v>1.6976</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9635999999999998</v>
+        <v>-9.9193</v>
       </c>
       <c r="M19" t="n">
-        <v>-21.6371</v>
+        <v>-4.1007</v>
       </c>
       <c r="N19" t="n">
-        <v>-13.3896</v>
+        <v>-3.2438</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.2476</v>
+        <v>-0.857</v>
       </c>
       <c r="P19" t="n">
-        <v>11.0056</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>-12.7433</v>
+        <v>-2.317</v>
       </c>
       <c r="R19" t="n">
-        <v>23.7486</v>
+        <v>4.8269</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.6753</v>
+        <v>-1.0483</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.0799</v>
+        <v>-0.4011999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-5.5953</v>
+        <v>-0.647</v>
       </c>
       <c r="V19" t="n">
-        <v>-5.807700000000001</v>
+        <v>-2.1272</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5133</v>
+        <v>-0.0426</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.321000000000001</v>
+        <v>-2.0845</v>
       </c>
     </row>
     <row r="20">
@@ -1969,16 +1969,16 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>27.9346</v>
+        <v>49.4503</v>
       </c>
       <c r="E20" t="n">
-        <v>84.79289999999999</v>
+        <v>92.51849999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-56.8588</v>
+        <v>-43.0683</v>
       </c>
       <c r="G20" t="n">
-        <v>33.91940000000001</v>
+        <v>33.9194</v>
       </c>
       <c r="H20" t="n">
         <v>66.8917</v>
@@ -1993,7 +1993,7 @@
         <v>228.7756</v>
       </c>
       <c r="L20" t="n">
-        <v>69.3814</v>
+        <v>69.38140000000001</v>
       </c>
       <c r="M20" t="n">
         <v>-264.2372</v>
@@ -2014,13 +2014,13 @@
         <v>366.8482</v>
       </c>
       <c r="S20" t="n">
-        <v>-42.60929999999999</v>
+        <v>-21.0943</v>
       </c>
       <c r="T20" t="n">
-        <v>-19.5291</v>
+        <v>-11.8036</v>
       </c>
       <c r="U20" t="n">
-        <v>-23.0802</v>
+        <v>-9.290100000000002</v>
       </c>
       <c r="V20" t="n">
         <v>25.0394</v>
